--- a/data/templates/계정별_필수절차_카탈로그_FY2026.xlsx
+++ b/data/templates/계정별_필수절차_카탈로그_FY2026.xlsx
@@ -425,21 +425,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,7 +560,6 @@
           <t>KSA505</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -593,50 +592,1578 @@
           <t>조회</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>A Lead</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>KSA505</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>매출채권</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>매출채권 외부조회</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>잔액&gt;PM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>조회서;회신;대사</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>confirmation;조회서</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>일치 또는 차이 해소</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ref만 있고 조회서 회신 없음</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KSA505</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>미회신 거래처 대체절차(입금확인·후속거래) 수행 근거 보완</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>매출채권</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>대손충당금 추정 근거</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>연령분석 존재</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>연령분석표;추정근거</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>연령분석;대손</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>충당금율;회수가능성</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>추정 근거·이력 데이터 제시</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>충당금율 산정 근거 없이 전기와 동일 비율 적용</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>K-IFRS1109 손상(기대신용손실)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>채권군별 회수 이력 기반 손상률 재산정 근거 보완</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>재고자산</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F1-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>재고 실사입회</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>재고자산&gt;PM</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>실사입회조서;실사일자;참관사진</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>실사입회</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>참관;입회</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>실사수량과 장부수량 대사 일치</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>E100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>실사입회 언급만 있고 실사일자·수량대사 기록 없음</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KSA501 재고자산 실사 입회</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>실사조서에 실사일자·표본수량·장부대사 기록 보완</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>재고자산</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F1-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>저가법(NRV) 검토</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>재고자산&gt;PM</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>품목별 단가;처분비용 추정;NRV계산표</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>저가법</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>순실현가능가치;NRV</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>품목별 NRV&lt;원가 여부 계산 근거 제시</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>E100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>저가법 검토 서술만 있고 NRV 계산 근거(단가·처분비용) 없음</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>K-IFRS1002 §28~33 / 일반기준 7장</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>품목별 순실현가능가치 계산표 작성 근거 보완</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>재고자산</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F1-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>진부화·장기재고 평가감</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>장기재고 존재</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>재고연령분석;평가감산정근거</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>진부화</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>장기재고;재고연령</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>연령별 평가감율 산정 근거 제시</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>E100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>저가법만 검토하고 진부화(장기재고) 별도 판단 없음</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4대중점 재고 저가법·진부화(L2/U2)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>재고 연령분석 및 진부화 평가감 근거 추가 검토</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>감가상각 재계산</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>당기 상각비&gt;PM*0.1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>자산대장;상각방법;내용연수</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>감가상각</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>재계산;검증</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>표본 재계산 오차 허용범위 내</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>상각방법·내용연수 변경이 있으나 재계산 검증 없음</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>K-IFRS1016 §60~62</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>표본 추출 재계산으로 상각비 검증 근거 보완</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>유형자산</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>E-02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>손상검사 트리거 검토</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>가동중단·시장가치 급락 등 손상지표</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>손상지표 점검표;회수가능액 추정</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>손상검사</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>회수가능액;사용가치</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>손상지표 없음 결론 근거 제시 또는 손상 인식</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>손상지표(가동중단 등)가 관찰되나 손상검사 결론 없음</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>K-IFRS1036</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>손상지표 점검표 작성 및 회수가능액 추정 근거 보완</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>E2-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>개발비 자산화 요건 검토</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>개발비 자산화 존재</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>자산화 4요건 점검표;기술적/경제적 실현가능성</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>개발비</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>자산화;연구비</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6가지 요건별 판단 근거 제시</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>개발비 자산화했으나 요건별 판단 근거 서술 없음</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>K-IFRS1038 §57</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>자산화 요건(기술적 실현가능성 등) 항목별 판단 근거 보완</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>무형자산</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>E2-02</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>무형자산 손상검사</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>비한정 내용연수 자산 또는 손상지표</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>회수가능액 추정;손상지표점검</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>손상;회수가능액</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>손상 없음 결론 근거 또는 손상 인식</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>비한정 내용연수 무형자산인데 연간 손상검사 누락</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>K-IFRS1038 §108, 1036</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>비한정 내용연수 자산 연간 손상검사 수행 근거 보완</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>투자자산</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F200-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>지분법 손상지표 검토</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>지분법적용투자주식 존재</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>피투자사 재무제표;손상지표점검표</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>지분법</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>손상지표;회수가능액</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>피투자사 재무제표 확보 및 손상지표 판단 근거 제시</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SAJ</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>피투자사 재무제표 미확보 또는 손상지표 판단 서술 없음</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>K-IFRS1028 §40~43</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>피투자사 최근 재무제표 확보 및 손상지표 점검 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>투자자산</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F200-02</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>지분법 손익 재계산</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>지분법손익 인식</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>지분율;피투자사 순이익;재계산근거</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>지분법이익;지분법손실</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>지분율×피투자사 순이익 재계산 일치</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SAJ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>지분법손익 금액 재계산 검증 없음</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>K-IFRS1028</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>지분율 기준 지분법손익 재계산 검증 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>차입금</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BB-02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>이자비용 재계산(이자테스트)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>차입금 존재</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>평균이자율;평균잔액;재계산표</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>이자테스트</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>평균이자율;재계산</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>재계산 이자비용과 장부금액 오차 허용범위 내</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BB200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>이자테스트 언급만 있고 평균잔액×이자율 재계산 근거 없음</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>KSA520 분석적 절차</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>평균잔액×이자율 재계산 근거표 작성 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>차입금</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BB-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>약정사항(covenant) 준수 검토</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>약정서 존재</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>약정서;재무비율산정근거</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>covenant;약정</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>약정 재무비율 준수 확인 근거 제시</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BB Lead</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>약정서는 확인했으나 재무비율 준수 여부 계산 없음</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>K-IFRS1001 §74~76(비유동 재분류)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>약정 재무비율 계산 및 위반 시 비유동 재분류 검토 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>충당부채</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CL-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>충당부채 추정 근거 재계산</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>충당부채 존재</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>산정근거;과거이력;확률가중</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>충당부채</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>추정근거;산정방법</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>합리적 추정 방법·이력 데이터 제시</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FF</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>충당부채 금액 산정 근거(추정방법) 서술 없음</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>K-IFRS1037 §36~52</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>최선의 추정치 산정방법(과거이력·확률가중 등) 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>우발부채</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CL-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>제공/수혜 보증 구분 및 주석대사</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>보증 존재</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>보증계약서;주석공시금액</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>보증;약정</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>제공/수혜 구분 명확·주석 금액 일치</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>제공보증과 수혜보증이 구분되지 않거나 주석 금액과 상이</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>K-IFRS1037 §86 우발부채 공시</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>제공/수혜 보증 구분 및 주석 공시금액 대사 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>수익인식 5단계 판단</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>복합계약·장기공사 등 특수거래</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>계약서;수행의무구분;인식시점판단</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>수익인식</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>수행의무;인식시점</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5단계(계약식별~수익인식) 판단 근거 제시</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>P/Q</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>복합계약이 있는데 수행의무별 배분 근거 없음</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>K-IFRS1115</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>계약별 수행의무 식별 및 수익인식 시점 판단 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>기간귀속(cut-off) 검토</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>기말 인근 매출 존재</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>선적일;인도일;출고증</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>cut-off;기간귀속</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>기말 전후 표본 대사로 귀속 오류 없음 확인</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>P/Q</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>기말 인근 매출 표본 cut-off 테스트 없음</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>KSA330 실증절차</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>기말 전후 매출 표본 선적·인도일 대사 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>법인세</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>이연법인세자산 실현가능성 검토</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>이연법인세자산 존재</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>미래과세소득추정;실현가능성판단</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>이연법인세</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>실현가능성;미래과세소득</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>미래 과세소득 추정 근거 제시</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>이연법인세자산 인식했으나 실현가능성 판단 근거 없음</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>K-IFRS1012 §34~36</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>미래 과세소득 추정 및 실현가능성 판단 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>법인세</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>세무조정 대사</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>세무조정 존재</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>세무조정계산서;영구/일시차이구분</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>세무조정;일시차이</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>세무조정계산서와 재무제표 법인세비용 대사 일치</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>세무조정계산서와 재무제표 법인세비용 간 대사 없음</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>법인세법·K-IFRS1012</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>세무조정계산서 기준 법인세비용 대사 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>자본</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>I-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>자본변동 및 배당 검토</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>배당·증자·감자 존재</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>주주총회의사록;이사회의사록</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>배당;증자;감자</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>법정절차(의사록) 근거 확인</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>배당·증자 등이 있으나 의사록 등 법정절차 근거 확인 없음</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>상법 및 K-IFRS1001</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>주주총회·이사회 의사록 등 법정절차 근거 확인 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>자본</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>I-02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>주식보상(주식선택권 등) 평가</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>주식보상 존재</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>평가모델;공정가치산정근거</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>주식보상;주식선택권</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>공정가치 평가모델 및 가정 근거 제시</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>주식보상비용 인식했으나 공정가치 산정 근거 없음</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>K-IFRS1102</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>옵션평가모델 가정 및 공정가치 산정 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>특수관계자</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>J-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>특수관계자 거래·잔액 완전성</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>특수관계자 존재</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>특수관계자목록;거래내역;약정서</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>특수관계자</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>관계회사;대여금</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>특수관계자 목록 최신화 및 거래 전건 확인 근거 제시</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>관계사 조서(계정 무관)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>특수관계자 목록 최신화 없이 전기 목록 재사용</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>K-IFRS1024</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>특수관계자 목록 최신화 및 거래·잔액 완전성 확인 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>특수관계자</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>J-02</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>대여금·보증 공시 검토</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>특수관계자 대여금 존재</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>대여계약서;이자율적정성;주석공시</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>대여금;지급보증</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>이자율 적정성 및 주석 공시 완전성 확인</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>관계사 조서(계정 무관)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>특수관계자 대여금 이자율 적정성 판단 없이 주석만 공시</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>4대중점 특수관계자 대여금·발행증권현황</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>대여금 이자율 적정성(정상가격) 판단 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>리스</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>K-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>사용권자산·리스부채 재계산</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>리스계약 존재</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>리스계약서;할인율;리스기간</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>사용권자산</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>리스부채;할인율</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>할인율·리스기간 근거 기반 재계산 일치</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>사용권자산·리스부채 최초 인식 재계산 검증 없음</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>K-IFRS1116 §26~28</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>리스 조건(기간·할인율) 기반 사용권자산·리스부채 재계산 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>리스</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>K-02</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>할인율 재검토 트리거 검토</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>리스 변경·재평가 사유 존재</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>증분차입이자율 산정근거</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>할인율;증분차입이자율</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>할인율 산정방법 및 재검토 필요성 판단 근거 제시</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>리스 변경이 있으나 할인율 재검토 판단 없음</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>K-IFRS1116 §40~46</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>리스 변경 시 할인율 재검토 판단 근거 보완</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>계속기업</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GC-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>계속기업 가정 지표 검토</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>자본잠식·순손실 지속 등 지표 존재</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>계속기업평가서;경영계획;자금조달계획</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>계속기업</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>자본잠식;순손실</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>유의적 의문 지표 점검 및 경영계획 근거 제시</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Lead 전체(계정 무관)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>계속기업 가정에 유의적 의문을 초래하는 지표가 있으나 평가 조서 없음</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>KSA570</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>계속기업 평가조서(지표점검·경영계획·자금조달계획) 작성 보완</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
